--- a/order_forms/050_trade_show_display_booth_order_form--order_forms.xlsx
+++ b/order_forms/050_trade_show_display_booth_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1001,_'label':_'standard_order',_'value':_'standard_order'}</t>
+          <t>standard_order</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1001, 'label': 'Standard Order', 'value': 'standard_order'}</t>
+          <t>Standard Order</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_1002,_'label':_'custom_order',_'value':_'custom_order'}</t>
+          <t>custom_order</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 1002, 'label': 'Custom Order', 'value': 'custom_order'}</t>
+          <t>Custom Order</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_2001,_'label':_'online',_'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 2001, 'label': 'Online', 'value': 'online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2002,_'label':_'offline',_'value':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2002, 'label': 'Offline', 'value': 'offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3001,_'label':_'new',_'value':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3001, 'label': 'New', 'value': 'new'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3002,_'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3002, 'label': 'In Progress', 'value': 'in_progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3003,_'label':_'delivered',_'value':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3003, 'label': 'Delivered', 'value': 'delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
